--- a/cfg/excel/ItemCfg.xlsx
+++ b/cfg/excel/ItemCfg.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="137">
   <si>
     <t>##var</t>
   </si>
@@ -96,7 +96,10 @@
     <t>string</t>
   </si>
   <si>
-    <t>(list#sep=,),int</t>
+    <t>ItemType</t>
+  </si>
+  <si>
+    <t>(list#sep=,),UseWay</t>
   </si>
   <si>
     <t>bool</t>
@@ -1551,10 +1554,10 @@
         <v>18</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>18</v>
@@ -1584,57 +1587,57 @@
         <v>17</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:17">
       <c r="A3" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" s="3" customFormat="1" customHeight="1" spans="1:17">
@@ -1643,21 +1646,21 @@
         <v>1</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E4" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J4" s="7">
         <v>0</v>
@@ -1676,21 +1679,21 @@
         <v>2</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E5" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J5" s="7">
         <v>0</v>
@@ -1709,20 +1712,20 @@
         <v>3</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E6" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3"/>
       <c r="H6" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J6" s="7">
         <v>0</v>
@@ -1741,21 +1744,21 @@
         <v>4</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E7" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J7" s="7">
         <v>0</v>
@@ -1774,21 +1777,21 @@
         <v>5</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E8" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J8" s="7">
         <v>0</v>
@@ -1807,21 +1810,21 @@
         <v>6</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E9" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J9" s="7">
         <v>0</v>
@@ -1840,21 +1843,21 @@
         <v>7</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E10" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
       <c r="H10" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J10" s="7">
         <v>0</v>
@@ -1872,21 +1875,21 @@
         <v>8</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E11" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J11" s="7">
         <v>0</v>
@@ -1898,21 +1901,21 @@
         <v>9</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E12" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J12" s="7">
         <v>0</v>
@@ -1924,21 +1927,21 @@
         <v>1008</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E13" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
       <c r="H13" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J13" s="7">
         <v>0</v>
@@ -1952,21 +1955,21 @@
         <v>1009</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E14" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
       <c r="H14" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J14" s="7">
         <v>0</v>
@@ -1980,21 +1983,21 @@
         <v>1010</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E15" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
       <c r="H15" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J15" s="7">
         <v>0</v>
@@ -2008,21 +2011,21 @@
         <v>1011</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E16" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
       <c r="H16" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J16" s="7">
         <v>0</v>
@@ -2036,21 +2039,21 @@
         <v>1012</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E17" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
       <c r="H17" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J17" s="7">
         <v>0</v>
@@ -2064,21 +2067,21 @@
         <v>1013</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E18" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
       <c r="H18" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J18" s="7">
         <v>0</v>
@@ -2092,19 +2095,19 @@
         <v>1014</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E19" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J19" s="7">
         <v>0</v>
@@ -2118,19 +2121,19 @@
         <v>1015</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E20" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J20" s="7">
         <v>1</v>
@@ -2144,19 +2147,19 @@
         <v>1016</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E21" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J21" s="7">
         <v>1</v>
@@ -2170,19 +2173,19 @@
         <v>1017</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E22" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J22" s="7">
         <v>1</v>
@@ -2196,19 +2199,19 @@
         <v>1018</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E23" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J23" s="7">
         <v>1</v>
@@ -2222,19 +2225,19 @@
         <v>1019</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E24" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J24" s="7">
         <v>1</v>
@@ -2248,19 +2251,19 @@
         <v>1020</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E25" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J25" s="7">
         <v>1</v>
@@ -2274,19 +2277,19 @@
         <v>1021</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E26" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J26" s="7">
         <v>2</v>
@@ -2300,19 +2303,19 @@
         <v>1022</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E27" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J27" s="7">
         <v>2</v>
@@ -2326,19 +2329,19 @@
         <v>1023</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E28" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J28" s="7">
         <v>2</v>
@@ -2352,19 +2355,19 @@
         <v>1024</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E29" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J29" s="7">
         <v>2</v>
@@ -2378,19 +2381,19 @@
         <v>1025</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E30" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J30" s="7">
         <v>2</v>
@@ -2404,19 +2407,19 @@
         <v>1026</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E31" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J31" s="7">
         <v>2</v>
@@ -2430,19 +2433,19 @@
         <v>1027</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E32" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J32" s="7">
         <v>3</v>
@@ -2456,19 +2459,19 @@
         <v>1028</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E33" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J33" s="7">
         <v>3</v>
@@ -2482,19 +2485,19 @@
         <v>1029</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E34" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J34" s="7">
         <v>3</v>
@@ -2508,19 +2511,19 @@
         <v>1030</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E35" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J35" s="7">
         <v>3</v>
@@ -2534,19 +2537,19 @@
         <v>1031</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E36" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J36" s="7">
         <v>3</v>
@@ -2560,19 +2563,19 @@
         <v>1032</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E37" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J37" s="7">
         <v>3</v>
@@ -2586,19 +2589,19 @@
         <v>1033</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E38" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J38" s="7">
         <v>4</v>
@@ -2612,19 +2615,19 @@
         <v>1034</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E39" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J39" s="7">
         <v>4</v>
@@ -2638,19 +2641,19 @@
         <v>1035</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E40" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J40" s="7">
         <v>4</v>
@@ -2664,19 +2667,19 @@
         <v>1036</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E41" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J41" s="7">
         <v>4</v>
@@ -2690,19 +2693,19 @@
         <v>1037</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E42" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J42" s="7">
         <v>4</v>
@@ -2716,19 +2719,19 @@
         <v>1038</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E43" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J43" s="7">
         <v>5</v>
@@ -2742,19 +2745,19 @@
         <v>1039</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E44" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J44" s="7">
         <v>5</v>
@@ -2768,19 +2771,19 @@
         <v>1040</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E45" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J45" s="7">
         <v>5</v>
@@ -2794,19 +2797,19 @@
         <v>1041</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E46" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J46" s="7">
         <v>5</v>
@@ -2820,16 +2823,16 @@
         <v>200101</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E47" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J47" s="8">
         <v>0</v>
@@ -2840,16 +2843,16 @@
         <v>200201</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E48" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J48" s="8">
         <v>2</v>
@@ -2860,16 +2863,16 @@
         <v>200301</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E49" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J49" s="8">
         <v>1</v>
@@ -2880,16 +2883,16 @@
         <v>200401</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E50" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J50" s="8">
         <v>2</v>
@@ -2900,16 +2903,16 @@
         <v>200501</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E51" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J51" s="8">
         <v>0</v>
@@ -2920,16 +2923,16 @@
         <v>200601</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E52" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J52" s="8">
         <v>3</v>
@@ -2940,16 +2943,16 @@
         <v>200701</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E53" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I53" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J53" s="8">
         <v>1</v>
@@ -2960,16 +2963,16 @@
         <v>200801</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E54" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J54" s="8">
         <v>3</v>

--- a/cfg/excel/ItemCfg.xlsx
+++ b/cfg/excel/ItemCfg.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\IdeaProjects\server-cluster\cfg\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\Shooting\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="140">
   <si>
     <t>##var</t>
   </si>
@@ -102,6 +102,9 @@
     <t>(list#sep=,),UseWay</t>
   </si>
   <si>
+    <t>vector2</t>
+  </si>
+  <si>
     <t>bool</t>
   </si>
   <si>
@@ -156,6 +159,9 @@
     <t>巡界币</t>
   </si>
   <si>
+    <t>Currency</t>
+  </si>
+  <si>
     <t>1,1</t>
   </si>
   <si>
@@ -181,6 +187,9 @@
   </si>
   <si>
     <t>荣誉分</t>
+  </si>
+  <si>
+    <t>Prop</t>
   </si>
   <si>
     <t>每一次任务巡界号都记得</t>
@@ -1566,7 +1575,7 @@
         <v>18</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>17</v>
@@ -1587,57 +1596,57 @@
         <v>17</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:17">
       <c r="A3" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" s="3" customFormat="1" customHeight="1" spans="1:17">
@@ -1646,21 +1655,21 @@
         <v>1</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="7">
-        <v>0</v>
+        <v>39</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J4" s="7">
         <v>0</v>
@@ -1679,21 +1688,21 @@
         <v>2</v>
       </c>
       <c r="C5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>40</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" s="7">
-        <v>0</v>
       </c>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J5" s="7">
         <v>0</v>
@@ -1712,20 +1721,20 @@
         <v>3</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" s="6">
-        <v>0</v>
+        <v>45</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>40</v>
       </c>
       <c r="F6" s="3"/>
       <c r="H6" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J6" s="7">
         <v>0</v>
@@ -1744,21 +1753,21 @@
         <v>4</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" s="6">
-        <v>0</v>
+        <v>47</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>40</v>
       </c>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J7" s="7">
         <v>0</v>
@@ -1777,21 +1786,21 @@
         <v>5</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E8" s="7">
-        <v>1</v>
+        <v>49</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J8" s="7">
         <v>0</v>
@@ -1810,21 +1819,21 @@
         <v>6</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" s="7">
-        <v>1</v>
+        <v>52</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J9" s="7">
         <v>0</v>
@@ -1843,21 +1852,21 @@
         <v>7</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" s="7">
-        <v>1</v>
+        <v>54</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
       <c r="H10" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J10" s="7">
         <v>0</v>
@@ -1875,21 +1884,21 @@
         <v>8</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" s="7">
-        <v>1</v>
+        <v>56</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J11" s="7">
         <v>0</v>
@@ -1901,21 +1910,21 @@
         <v>9</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E12" s="7">
-        <v>1</v>
+        <v>58</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J12" s="7">
         <v>0</v>
@@ -1927,21 +1936,21 @@
         <v>1008</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" s="7">
-        <v>1</v>
+        <v>60</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
       <c r="H13" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J13" s="7">
         <v>0</v>
@@ -1955,21 +1964,21 @@
         <v>1009</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E14" s="7">
-        <v>1</v>
+        <v>64</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
       <c r="H14" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J14" s="7">
         <v>0</v>
@@ -1983,21 +1992,21 @@
         <v>1010</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E15" s="7">
-        <v>1</v>
+        <v>66</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
       <c r="H15" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J15" s="7">
         <v>0</v>
@@ -2011,21 +2020,21 @@
         <v>1011</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16" s="7">
-        <v>1</v>
+        <v>68</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
       <c r="H16" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J16" s="7">
         <v>0</v>
@@ -2039,21 +2048,21 @@
         <v>1012</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E17" s="7">
-        <v>1</v>
+        <v>70</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
       <c r="H17" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J17" s="7">
         <v>0</v>
@@ -2067,21 +2076,21 @@
         <v>1013</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="E18" s="7">
-        <v>1</v>
+        <v>72</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
       <c r="H18" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J18" s="7">
         <v>0</v>
@@ -2095,19 +2104,19 @@
         <v>1014</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E19" s="7">
-        <v>1</v>
+        <v>74</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J19" s="7">
         <v>0</v>
@@ -2121,19 +2130,19 @@
         <v>1015</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1</v>
+        <v>76</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J20" s="7">
         <v>1</v>
@@ -2147,19 +2156,19 @@
         <v>1016</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E21" s="7">
-        <v>1</v>
+        <v>78</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J21" s="7">
         <v>1</v>
@@ -2173,19 +2182,19 @@
         <v>1017</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E22" s="7">
-        <v>1</v>
+        <v>80</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J22" s="7">
         <v>1</v>
@@ -2199,19 +2208,19 @@
         <v>1018</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="E23" s="7">
-        <v>1</v>
+        <v>82</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J23" s="7">
         <v>1</v>
@@ -2225,19 +2234,19 @@
         <v>1019</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E24" s="7">
-        <v>1</v>
+        <v>84</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J24" s="7">
         <v>1</v>
@@ -2251,19 +2260,19 @@
         <v>1020</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="E25" s="7">
-        <v>1</v>
+        <v>87</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J25" s="7">
         <v>1</v>
@@ -2277,19 +2286,19 @@
         <v>1021</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="I26" s="7" t="s">
         <v>85</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="E26" s="7">
-        <v>1</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>82</v>
       </c>
       <c r="J26" s="7">
         <v>2</v>
@@ -2303,19 +2312,19 @@
         <v>1022</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E27" s="7">
-        <v>1</v>
+        <v>91</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J27" s="7">
         <v>2</v>
@@ -2329,19 +2338,19 @@
         <v>1023</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="E28" s="7">
-        <v>1</v>
+        <v>93</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="J28" s="7">
         <v>2</v>
@@ -2355,19 +2364,19 @@
         <v>1024</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="E29" s="7">
-        <v>1</v>
+        <v>96</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J29" s="7">
         <v>2</v>
@@ -2381,19 +2390,19 @@
         <v>1025</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E30" s="7">
-        <v>1</v>
+        <v>98</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="J30" s="7">
         <v>2</v>
@@ -2407,19 +2416,19 @@
         <v>1026</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="E31" s="7">
-        <v>1</v>
+        <v>101</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J31" s="7">
         <v>2</v>
@@ -2433,19 +2442,19 @@
         <v>1027</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="E32" s="7">
-        <v>1</v>
+        <v>103</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J32" s="7">
         <v>3</v>
@@ -2459,19 +2468,19 @@
         <v>1028</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="E33" s="7">
-        <v>1</v>
+        <v>105</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J33" s="7">
         <v>3</v>
@@ -2485,19 +2494,19 @@
         <v>1029</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="E34" s="7">
-        <v>1</v>
+        <v>107</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J34" s="7">
         <v>3</v>
@@ -2511,19 +2520,19 @@
         <v>1030</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E35" s="7">
-        <v>1</v>
+        <v>109</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J35" s="7">
         <v>3</v>
@@ -2537,19 +2546,19 @@
         <v>1031</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="E36" s="7">
-        <v>1</v>
+        <v>111</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J36" s="7">
         <v>3</v>
@@ -2563,19 +2572,19 @@
         <v>1032</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="E37" s="7">
-        <v>1</v>
+        <v>113</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="J37" s="7">
         <v>3</v>
@@ -2589,19 +2598,19 @@
         <v>1033</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="E38" s="7">
-        <v>1</v>
+        <v>115</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J38" s="7">
         <v>4</v>
@@ -2615,19 +2624,19 @@
         <v>1034</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="E39" s="7">
-        <v>1</v>
+        <v>117</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J39" s="7">
         <v>4</v>
@@ -2641,19 +2650,19 @@
         <v>1035</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="E40" s="7">
-        <v>1</v>
+        <v>119</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J40" s="7">
         <v>4</v>
@@ -2667,19 +2676,19 @@
         <v>1036</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="E41" s="7">
-        <v>1</v>
+        <v>121</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J41" s="7">
         <v>4</v>
@@ -2693,19 +2702,19 @@
         <v>1037</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="E42" s="7">
-        <v>1</v>
+        <v>123</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J42" s="7">
         <v>4</v>
@@ -2719,19 +2728,19 @@
         <v>1038</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="E43" s="7">
-        <v>1</v>
+        <v>125</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J43" s="7">
         <v>5</v>
@@ -2745,19 +2754,19 @@
         <v>1039</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="E44" s="7">
-        <v>1</v>
+        <v>127</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J44" s="7">
         <v>5</v>
@@ -2771,19 +2780,19 @@
         <v>1040</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="E45" s="7">
-        <v>1</v>
+        <v>129</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J45" s="7">
         <v>5</v>
@@ -2797,19 +2806,19 @@
         <v>1041</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="E46" s="7">
-        <v>1</v>
+        <v>131</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J46" s="7">
         <v>5</v>
@@ -2823,16 +2832,16 @@
         <v>200101</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="E47" s="7">
-        <v>1</v>
+        <v>132</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J47" s="8">
         <v>0</v>
@@ -2843,16 +2852,16 @@
         <v>200201</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="E48" s="7">
-        <v>1</v>
+        <v>133</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J48" s="8">
         <v>2</v>
@@ -2863,16 +2872,16 @@
         <v>200301</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="E49" s="7">
-        <v>1</v>
+        <v>134</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J49" s="8">
         <v>1</v>
@@ -2883,16 +2892,16 @@
         <v>200401</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="E50" s="7">
-        <v>1</v>
+        <v>135</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J50" s="8">
         <v>2</v>
@@ -2903,16 +2912,16 @@
         <v>200501</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="E51" s="7">
-        <v>1</v>
+        <v>136</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J51" s="8">
         <v>0</v>
@@ -2923,16 +2932,16 @@
         <v>200601</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="E52" s="7">
-        <v>1</v>
+        <v>137</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J52" s="8">
         <v>3</v>
@@ -2943,16 +2952,16 @@
         <v>200701</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="E53" s="7">
-        <v>1</v>
+        <v>138</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I53" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J53" s="8">
         <v>1</v>
@@ -2963,16 +2972,16 @@
         <v>200801</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="E54" s="7">
-        <v>1</v>
+        <v>139</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J54" s="8">
         <v>3</v>
